--- a/database/event/4240/event_4240_evp_summary.xlsx
+++ b/database/event/4240/event_4240_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.2726</v>
+        <v>12.2569</v>
       </c>
       <c r="C2" t="n">
-        <v>4.4844</v>
+        <v>4.4786</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5365</v>
+        <v>4.4392</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2726</v>
+        <v>12.2569</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6705</v>
+        <v>5.6548</v>
       </c>
       <c r="G2" t="n">
         <v>6.6021</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5883</v>
+        <v>6.5637</v>
       </c>
       <c r="I2" t="n">
         <v>6.619</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.5533</v>
+        <v>10.5414</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8561</v>
+        <v>3.8518</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8419</v>
+        <v>3.7558</v>
       </c>
       <c r="E3" t="n">
-        <v>10.5533</v>
+        <v>10.5414</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6544</v>
+        <v>4.6425</v>
       </c>
       <c r="G3" t="n">
         <v>5.8989</v>
       </c>
       <c r="H3" t="n">
-        <v>4.995</v>
+        <v>4.9764</v>
       </c>
       <c r="I3" t="n">
         <v>5.0182</v>
@@ -594,7 +594,7 @@
         <v>2.6739</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5349</v>
+        <v>2.4715</v>
       </c>
       <c r="E4" t="n">
         <v>7.3179</v>
@@ -640,7 +640,7 @@
         <v>2.6294</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4857</v>
+        <v>2.423</v>
       </c>
       <c r="E5" t="n">
         <v>7.196</v>
@@ -686,7 +686,7 @@
         <v>2.5771</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4278</v>
+        <v>2.3659</v>
       </c>
       <c r="E6" t="n">
         <v>7.0528</v>
@@ -732,7 +732,7 @@
         <v>2.0444</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8389</v>
+        <v>1.7851</v>
       </c>
       <c r="E7" t="n">
         <v>5.595</v>
@@ -778,7 +778,7 @@
         <v>2.0222</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8143</v>
+        <v>1.7609</v>
       </c>
       <c r="E8" t="n">
         <v>5.5342</v>
@@ -824,7 +824,7 @@
         <v>1.9603</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7459</v>
+        <v>1.6934</v>
       </c>
       <c r="E9" t="n">
         <v>5.3648</v>
@@ -870,7 +870,7 @@
         <v>1.9235</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7052</v>
+        <v>1.6533</v>
       </c>
       <c r="E10" t="n">
         <v>5.2641</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.2493</v>
+        <v>5.2392</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9181</v>
+        <v>1.9144</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6992</v>
+        <v>1.6434</v>
       </c>
       <c r="E11" t="n">
-        <v>5.2493</v>
+        <v>5.2392</v>
       </c>
       <c r="F11" t="n">
-        <v>2.703</v>
+        <v>2.6929</v>
       </c>
       <c r="G11" t="n">
         <v>2.5463</v>
       </c>
       <c r="H11" t="n">
-        <v>2.703</v>
+        <v>2.6929</v>
       </c>
       <c r="I11" t="n">
         <v>2.7156</v>
@@ -962,7 +962,7 @@
         <v>1.818</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5885</v>
+        <v>1.5382</v>
       </c>
       <c r="E12" t="n">
         <v>4.9753</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.7638</v>
+        <v>4.7506</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7407</v>
+        <v>1.7359</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5031</v>
+        <v>1.4487</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7638</v>
+        <v>4.7506</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5231</v>
+        <v>3.5099</v>
       </c>
       <c r="G13" t="n">
         <v>1.2407</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5231</v>
+        <v>3.5099</v>
       </c>
       <c r="I13" t="n">
         <v>3.5395</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.7404</v>
+        <v>4.7112</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7321</v>
+        <v>1.7215</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4937</v>
+        <v>1.433</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7404</v>
+        <v>4.7112</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3857</v>
+        <v>5.3565</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6453</v>
       </c>
       <c r="H14" t="n">
-        <v>6.1417</v>
+        <v>6.0959</v>
       </c>
       <c r="I14" t="n">
         <v>6.199</v>
@@ -1100,7 +1100,7 @@
         <v>1.6667</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4213</v>
+        <v>1.3733</v>
       </c>
       <c r="E15" t="n">
         <v>4.5613</v>
@@ -1146,7 +1146,7 @@
         <v>1.622</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3719</v>
+        <v>1.3246</v>
       </c>
       <c r="E16" t="n">
         <v>4.439</v>
@@ -1192,7 +1192,7 @@
         <v>1.6135</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3625</v>
+        <v>1.3153</v>
       </c>
       <c r="E17" t="n">
         <v>4.4158</v>
@@ -1238,7 +1238,7 @@
         <v>1.5602</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3035</v>
+        <v>1.2572</v>
       </c>
       <c r="E18" t="n">
         <v>4.2698</v>
@@ -1284,7 +1284,7 @@
         <v>1.5206</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2598</v>
+        <v>1.2141</v>
       </c>
       <c r="E19" t="n">
         <v>4.1616</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.1336</v>
+        <v>4.1133</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5104</v>
+        <v>1.503</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2485</v>
+        <v>1.1948</v>
       </c>
       <c r="E20" t="n">
-        <v>4.1336</v>
+        <v>4.1133</v>
       </c>
       <c r="F20" t="n">
-        <v>4.1919</v>
+        <v>4.1716</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0583</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2698</v>
+        <v>4.238</v>
       </c>
       <c r="I20" t="n">
         <v>4.3097</v>
@@ -1376,7 +1376,7 @@
         <v>1.2971</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0127</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>3.5498</v>
@@ -1422,7 +1422,7 @@
         <v>1.2819</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9959</v>
+        <v>0.9538</v>
       </c>
       <c r="E22" t="n">
         <v>3.5082</v>
@@ -1468,7 +1468,7 @@
         <v>1.2627</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9747</v>
+        <v>0.9328</v>
       </c>
       <c r="E23" t="n">
         <v>3.4557</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7819</v>
+        <v>2.7708</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0165</v>
+        <v>1.0124</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7025</v>
+        <v>0.66</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7819</v>
+        <v>2.7708</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9917</v>
+        <v>2.9806</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2098</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9917</v>
+        <v>2.9806</v>
       </c>
       <c r="I24" t="n">
         <v>3.0057</v>
@@ -1560,7 +1560,7 @@
         <v>0.8749</v>
       </c>
       <c r="D25" t="n">
-        <v>0.546</v>
+        <v>0.5101</v>
       </c>
       <c r="E25" t="n">
         <v>2.3945</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.346</v>
+        <v>2.3211</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8572</v>
+        <v>0.8481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5264</v>
+        <v>0.4808</v>
       </c>
       <c r="E26" t="n">
-        <v>2.346</v>
+        <v>2.3211</v>
       </c>
       <c r="F26" t="n">
-        <v>3.346</v>
+        <v>3.3211</v>
       </c>
       <c r="G26" t="n">
         <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>3.346</v>
+        <v>3.3211</v>
       </c>
       <c r="I26" t="n">
         <v>3.3772</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1612</v>
+        <v>2.1609</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7897</v>
+        <v>0.7896</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4517</v>
+        <v>0.417</v>
       </c>
       <c r="E27" t="n">
-        <v>2.1612</v>
+        <v>2.1609</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0663</v>
+        <v>0.066</v>
       </c>
       <c r="G27" t="n">
         <v>2.0949</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0663</v>
+        <v>0.066</v>
       </c>
       <c r="I27" t="n">
         <v>0.06660000000000001</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.0893</v>
+        <v>2.0725</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7634</v>
+        <v>0.7573</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4227</v>
+        <v>0.3818</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0893</v>
+        <v>2.0725</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2473</v>
+        <v>2.2305</v>
       </c>
       <c r="G28" t="n">
         <v>-0.158</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2473</v>
+        <v>2.2305</v>
       </c>
       <c r="I28" t="n">
         <v>2.2682</v>
@@ -1744,7 +1744,7 @@
         <v>0.735</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3913</v>
+        <v>0.3575</v>
       </c>
       <c r="E29" t="n">
         <v>2.0116</v>
@@ -1790,7 +1790,7 @@
         <v>0.6796</v>
       </c>
       <c r="D30" t="n">
-        <v>0.33</v>
+        <v>0.2971</v>
       </c>
       <c r="E30" t="n">
         <v>1.86</v>
@@ -1836,7 +1836,7 @@
         <v>0.6717</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3212</v>
+        <v>0.2884</v>
       </c>
       <c r="E31" t="n">
         <v>1.8382</v>
@@ -1882,7 +1882,7 @@
         <v>0.6393</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2854</v>
+        <v>0.2531</v>
       </c>
       <c r="E32" t="n">
         <v>1.7496</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6674</v>
+        <v>1.6596</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6093</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2522</v>
+        <v>0.2173</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6674</v>
+        <v>1.6596</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0747</v>
+        <v>2.0669</v>
       </c>
       <c r="G33" t="n">
         <v>-0.4073</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0747</v>
+        <v>2.0669</v>
       </c>
       <c r="I33" t="n">
         <v>2.0843</v>
@@ -1974,7 +1974,7 @@
         <v>0.6017</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2439</v>
+        <v>0.2122</v>
       </c>
       <c r="E34" t="n">
         <v>1.6468</v>
@@ -2020,7 +2020,7 @@
         <v>0.5847</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2251</v>
+        <v>0.1936</v>
       </c>
       <c r="E35" t="n">
         <v>1.6003</v>
@@ -2066,7 +2066,7 @@
         <v>0.5641</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2023</v>
+        <v>0.1711</v>
       </c>
       <c r="E36" t="n">
         <v>1.5437</v>
@@ -2112,7 +2112,7 @@
         <v>0.4767</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1057</v>
+        <v>0.0759</v>
       </c>
       <c r="E37" t="n">
         <v>1.3047</v>
@@ -2158,7 +2158,7 @@
         <v>0.4019</v>
       </c>
       <c r="D38" t="n">
-        <v>0.023</v>
+        <v>-0.0057</v>
       </c>
       <c r="E38" t="n">
         <v>1.0999</v>
@@ -2204,7 +2204,7 @@
         <v>0.3935</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0136</v>
+        <v>-0.0149</v>
       </c>
       <c r="E39" t="n">
         <v>1.0768</v>
@@ -2250,7 +2250,7 @@
         <v>0.3703</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0119</v>
+        <v>-0.0401</v>
       </c>
       <c r="E40" t="n">
         <v>1.0135</v>
@@ -2296,7 +2296,7 @@
         <v>0.3455</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0394</v>
+        <v>-0.0672</v>
       </c>
       <c r="E41" t="n">
         <v>0.9456</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9288</v>
       </c>
       <c r="C42" t="n">
-        <v>0.342</v>
+        <v>0.3394</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0432</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9288</v>
       </c>
       <c r="F42" t="n">
-        <v>1.936</v>
+        <v>1.9288</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>1.936</v>
+        <v>1.9288</v>
       </c>
       <c r="I42" t="n">
         <v>1.945</v>
@@ -2388,7 +2388,7 @@
         <v>0.3274</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0594</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="E43" t="n">
         <v>0.896</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7984</v>
+        <v>0.7869</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2917</v>
+        <v>0.2875</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0988</v>
+        <v>-0.1304</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7984</v>
+        <v>0.7869</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5443</v>
+        <v>1.5328</v>
       </c>
       <c r="G44" t="n">
         <v>-0.7459</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5443</v>
+        <v>1.5328</v>
       </c>
       <c r="I44" t="n">
         <v>1.5587</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6679</v>
+        <v>0.6612</v>
       </c>
       <c r="C45" t="n">
-        <v>0.244</v>
+        <v>0.2416</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1515</v>
+        <v>-0.1805</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6679</v>
+        <v>0.6612</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8959</v>
+        <v>0.8892</v>
       </c>
       <c r="G45" t="n">
         <v>-0.228</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8959</v>
+        <v>0.8892</v>
       </c>
       <c r="I45" t="n">
         <v>0.9042</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5891</v>
+        <v>0.5869</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2153</v>
+        <v>0.2145</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1834</v>
+        <v>-0.2101</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5891</v>
+        <v>0.5869</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5951</v>
+        <v>0.5929</v>
       </c>
       <c r="G46" t="n">
         <v>-0.006</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5951</v>
+        <v>0.5929</v>
       </c>
       <c r="I46" t="n">
         <v>0.5979</v>
@@ -2572,7 +2572,7 @@
         <v>0.1836</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2183</v>
+        <v>-0.2437</v>
       </c>
       <c r="E47" t="n">
         <v>0.5026</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4592</v>
+        <v>0.4483</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1678</v>
+        <v>0.1638</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2359</v>
+        <v>-0.2653</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4592</v>
+        <v>0.4483</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4592</v>
+        <v>1.4483</v>
       </c>
       <c r="G48" t="n">
         <v>-1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.4592</v>
+        <v>1.4483</v>
       </c>
       <c r="I48" t="n">
         <v>1.4728</v>
@@ -2664,7 +2664,7 @@
         <v>0.1489</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2568</v>
+        <v>-0.2816</v>
       </c>
       <c r="E49" t="n">
         <v>0.4074</v>
@@ -2710,7 +2710,7 @@
         <v>0.1042</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3062</v>
+        <v>-0.3303</v>
       </c>
       <c r="E50" t="n">
         <v>0.2851</v>
@@ -2756,7 +2756,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3418</v>
+        <v>-0.3655</v>
       </c>
       <c r="E51" t="n">
         <v>0.1969</v>
@@ -2802,7 +2802,7 @@
         <v>0.0594</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3557</v>
+        <v>-0.3792</v>
       </c>
       <c r="E52" t="n">
         <v>0.1625</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0402</v>
+        <v>-0.0474</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0147</v>
+        <v>-0.0173</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4376</v>
+        <v>-0.4628</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0402</v>
+        <v>-0.0474</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9598</v>
+        <v>0.9526</v>
       </c>
       <c r="G53" t="n">
         <v>-1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9598</v>
+        <v>0.9526</v>
       </c>
       <c r="I53" t="n">
         <v>0.9687</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0523</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4792</v>
+        <v>-0.501</v>
       </c>
       <c r="E54" t="n">
         <v>-0.1432</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0608</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4885</v>
+        <v>-0.5102</v>
       </c>
       <c r="E55" t="n">
         <v>-0.1663</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0738</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5029</v>
+        <v>-0.5243</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2019</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0949</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5263</v>
+        <v>-0.5474</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2597</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1041</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5365</v>
+        <v>-0.5575</v>
       </c>
       <c r="E58" t="n">
         <v>-0.285</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3572</v>
+        <v>-0.3596</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1305</v>
+        <v>-0.1314</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5657</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3572</v>
+        <v>-0.3596</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6572</v>
+        <v>0.6548</v>
       </c>
       <c r="G59" t="n">
         <v>-1.0144</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6572</v>
+        <v>0.6548</v>
       </c>
       <c r="I59" t="n">
         <v>0.6603</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1508</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5881</v>
+        <v>-0.6083</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4127</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1973</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6395</v>
+        <v>-0.659</v>
       </c>
       <c r="E61" t="n">
         <v>-0.54</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1994</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6418</v>
+        <v>-0.6613</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5457</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5961</v>
+        <v>-0.594</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2178</v>
+        <v>-0.217</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6622</v>
+        <v>-0.6806</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5961</v>
+        <v>-0.594</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2781</v>
+        <v>-0.276</v>
       </c>
       <c r="G63" t="n">
         <v>-0.318</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2781</v>
+        <v>-0.276</v>
       </c>
       <c r="I63" t="n">
         <v>-0.2807</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2282</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6736</v>
+        <v>-0.6927</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6245000000000001</v>
@@ -3400,7 +3400,7 @@
         <v>-0.233</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.6979</v>
       </c>
       <c r="E65" t="n">
         <v>-0.6375999999999999</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6627</v>
+        <v>-0.6566</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2421</v>
+        <v>-0.2399</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6891</v>
+        <v>-0.7055</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6627</v>
+        <v>-0.6566</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="G66" t="n">
         <v>0.1594</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="I66" t="n">
         <v>-0.8298</v>
@@ -3492,7 +3492,7 @@
         <v>-0.2775</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7282</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="E67" t="n">
         <v>-0.7595</v>
@@ -3538,7 +3538,7 @@
         <v>-0.2848</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7362</v>
+        <v>-0.7544</v>
       </c>
       <c r="E68" t="n">
         <v>-0.7793</v>
@@ -3584,7 +3584,7 @@
         <v>-0.347</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.805</v>
+        <v>-0.8223</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9497</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4311</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.898</v>
+        <v>-0.9139</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1798</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4909</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9641</v>
+        <v>-0.9791</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3434</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5261</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.003</v>
+        <v>-1.0175</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4397</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5580000000000001</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0382</v>
+        <v>-1.0523</v>
       </c>
       <c r="E73" t="n">
         <v>-1.527</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7057</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2015</v>
+        <v>-1.2133</v>
       </c>
       <c r="E74" t="n">
         <v>-1.9312</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7344000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2333</v>
+        <v>-1.2446</v>
       </c>
       <c r="E75" t="n">
         <v>-2.0098</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7385</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2378</v>
+        <v>-1.2491</v>
       </c>
       <c r="E76" t="n">
         <v>-2.021</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7655</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2677</v>
+        <v>-1.2785</v>
       </c>
       <c r="E77" t="n">
         <v>-2.0949</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8353</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3449</v>
+        <v>-1.3547</v>
       </c>
       <c r="E78" t="n">
         <v>-2.2861</v>
@@ -4044,7 +4044,7 @@
         <v>-0.9433</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4643</v>
+        <v>-1.4725</v>
       </c>
       <c r="E79" t="n">
         <v>-2.5817</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0511</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5835</v>
+        <v>-1.59</v>
       </c>
       <c r="E80" t="n">
         <v>-2.8767</v>
@@ -4136,7 +4136,7 @@
         <v>-1.1611</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7051</v>
+        <v>-1.7099</v>
       </c>
       <c r="E81" t="n">
         <v>-3.1777</v>
@@ -4182,7 +4182,7 @@
         <v>-1.5738</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.1613</v>
+        <v>-2.1599</v>
       </c>
       <c r="E82" t="n">
         <v>-4.3071</v>
